--- a/artfynd/A 4553-2021 artfynd.xlsx
+++ b/artfynd/A 4553-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4553-2021 artfynd.xlsx
+++ b/artfynd/A 4553-2021 artfynd.xlsx
@@ -3171,10 +3171,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120976766</v>
+        <v>120976767</v>
       </c>
       <c r="B24" t="n">
-        <v>79680</v>
+        <v>79682</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3187,21 +3187,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120976767</v>
+        <v>120976766</v>
       </c>
       <c r="B25" t="n">
-        <v>79679</v>
+        <v>79683</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3289,21 +3289,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>

--- a/artfynd/A 4553-2021 artfynd.xlsx
+++ b/artfynd/A 4553-2021 artfynd.xlsx
@@ -3171,10 +3171,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120976767</v>
+        <v>120976766</v>
       </c>
       <c r="B24" t="n">
-        <v>79682</v>
+        <v>79683</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3187,21 +3187,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120976766</v>
+        <v>120976767</v>
       </c>
       <c r="B25" t="n">
-        <v>79683</v>
+        <v>79682</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3289,21 +3289,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>

--- a/artfynd/A 4553-2021 artfynd.xlsx
+++ b/artfynd/A 4553-2021 artfynd.xlsx
@@ -3171,10 +3171,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120976766</v>
+        <v>120976767</v>
       </c>
       <c r="B24" t="n">
-        <v>79683</v>
+        <v>79685</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3187,21 +3187,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3273,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120976767</v>
+        <v>120976766</v>
       </c>
       <c r="B25" t="n">
-        <v>79682</v>
+        <v>79686</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3289,21 +3289,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
